--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -23,13 +23,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFReligion</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFReligion</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:56:35+00:00</t>
+    <t>2023-11-09T22:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +80,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet VF_Religion</t>
+    <t>Use the link in the Expansion section to navigate to the ConceptMap.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +80,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Use the link in the Expansion section to navigate to the ConceptMap.</t>
+    <t>Navigate to the [ConceptMap VF_Religion](ConceptMap-CMVFReligion.html).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
+    <sheet name="Include from 2-.08" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="199">
   <si>
     <t>Property</t>
   </si>
@@ -35,28 +36,28 @@
     <t>Name</t>
   </si>
   <si>
+    <t>VSVFReligion</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
     <t>VF_Religion</t>
   </si>
   <si>
-    <t>Title</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Navigate to the [ConceptMap VF_Religion](ConceptMap-CMVFReligion.html).</t>
+    <t>Navigate to [ConceptMap VF_Religion](ConceptMap-CMVFReligion.html)</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -93,6 +94,522 @@
   </si>
   <si>
     <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>ADVENTIST</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>AFRICAN RELIGIONS</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>AFRO-CARIBBEAN RELIGIONS</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>AGNOSTICISM</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>ANGLICAN</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>ANIMISM</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>ASSEMBLY OF GOD</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>ATHEISM</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>BABI &amp;amp; BAHA'I FAITHS</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>BAPTIST</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>BON</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>BRETHREN</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>CAO DAI</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>CELTICISM</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>CHRISTIAN (NON-SPECIFIC)</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>CHRISTIAN SCIENTIST</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>CHURCH OF CHRIST</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>CHURCH OF GOD</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>CONFUCIANISM</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>CONGREGATIONAL</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>CYBERCULTURE RELIGIONS</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>DISCIPLES OF CHRIST</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>DIVINATION</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>EASTERN ORTHODOX</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>EPISCOPALIAN</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>EVANGELICAL COVENANT</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>FOURTH WAY</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>FREE DAISM</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>FRIENDS</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>FULL GOSPEL</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>GNOSIS</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>HINDUISM</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>HUMANISM</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>INDEPENDENT</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>ISLAM</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>JAINISM</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>JEHOVAH'S WITNESSES</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>JUDAISM</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>LATTER DAY SAINTS</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>LUTHERAN</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>MAHAYANA</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>MEDITATION</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>MESSIANIC JUDAISM</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>METHODIST</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>MITRAISM</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>NATIVE AMERICAN</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>NAZARENE</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>NEW AGE</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>NON-ROMAN CATHOLIC</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>OCCULT</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>ORTHODOX</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>PAGANISM</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>PENTECOSTAL</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>PRESBYTERIAN</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>PROCESS, THE</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>PROTESTANT</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>PROTESTANT, NO DENOMINATION</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>REFORMED</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>REFORMED/PRESBYTERIAN</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>ROMAN CATHOLIC CHURCH</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>SALVATION ARMY</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>SATANISM</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>SCIENTOLOGY</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>SHAMANISM</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>SHIITE (ISLAM)</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>SHINTO</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>SIKISM</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>SPIRITUALISM</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>SUNNI (ISLAM)</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>TAOISM</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>THERAVADA</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>UNITARIAN-UNIVERSALISM</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>UNITED CHURCH OF CHRIST</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>UNIVERSAL LIFE CHURCH</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>VAJRAYANA (TIBETAN)</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>VEDA</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>VOODOO</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>WICCA</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>YAOHUSHUA</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>ZEN BUDDHISM</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>ZOROASTRIANISM</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>ASKED BUT DECLINED TO ANSWER</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>UNKNOWN/NO PREFERENCE</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://va.gov/terminology/vistaDefinedElements/2-.08</t>
   </si>
 </sst>
 </file>
@@ -270,24 +787,22 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s" s="2">
         <v>12</v>
       </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -347,6 +862,716 @@
       </c>
       <c r="B15" t="s" s="2">
         <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B87"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="200">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -802,66 +805,68 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -880,698 +885,698 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -8,12 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from 2-.08" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from Religious Affili" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from NullFlavor" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="369">
   <si>
     <t>Property</t>
   </si>
@@ -30,21 +32,18 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>VSVFReligion</t>
+    <t>VF_Religion</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>VF_Religion</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -60,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -613,6 +612,516 @@
   </si>
   <si>
     <t>http://va.gov/terminology/vistaDefinedElements/2-.08</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>Adventist</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>African Religions</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>Afro-Caribbean Religions</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>Agnosticism</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>Anglican</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>Animism</t>
+  </si>
+  <si>
+    <t>1061</t>
+  </si>
+  <si>
+    <t>Assembly of God</t>
+  </si>
+  <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>Atheism</t>
+  </si>
+  <si>
+    <t>1008</t>
+  </si>
+  <si>
+    <t>Babi &amp; Baha'I faiths</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>Baptist</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>Bon</t>
+  </si>
+  <si>
+    <t>1062</t>
+  </si>
+  <si>
+    <t>Brethren</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>Cao Dai</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>Celticism</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>Christian (non-Catholic, non-specific)</t>
+  </si>
+  <si>
+    <t>1063</t>
+  </si>
+  <si>
+    <t>Christian Scientist</t>
+  </si>
+  <si>
+    <t>1064</t>
+  </si>
+  <si>
+    <t>Church of Christ</t>
+  </si>
+  <si>
+    <t>1065</t>
+  </si>
+  <si>
+    <t>Church of God</t>
+  </si>
+  <si>
+    <t>1014</t>
+  </si>
+  <si>
+    <t>Confucianism</t>
+  </si>
+  <si>
+    <t>1066</t>
+  </si>
+  <si>
+    <t>Congregational</t>
+  </si>
+  <si>
+    <t>1015</t>
+  </si>
+  <si>
+    <t>Cyberculture Religions</t>
+  </si>
+  <si>
+    <t>1067</t>
+  </si>
+  <si>
+    <t>Disciples of Christ</t>
+  </si>
+  <si>
+    <t>1016</t>
+  </si>
+  <si>
+    <t>Divination</t>
+  </si>
+  <si>
+    <t>1068</t>
+  </si>
+  <si>
+    <t>Eastern Orthodox</t>
+  </si>
+  <si>
+    <t>1069</t>
+  </si>
+  <si>
+    <t>Episcopalian</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Evangelical Covenant</t>
+  </si>
+  <si>
+    <t>1017</t>
+  </si>
+  <si>
+    <t>Fourth Way</t>
+  </si>
+  <si>
+    <t>1018</t>
+  </si>
+  <si>
+    <t>Free Daism</t>
+  </si>
+  <si>
+    <t>1071</t>
+  </si>
+  <si>
+    <t>Friends</t>
+  </si>
+  <si>
+    <t>1072</t>
+  </si>
+  <si>
+    <t>Full Gospel</t>
+  </si>
+  <si>
+    <t>1019</t>
+  </si>
+  <si>
+    <t>Gnosis</t>
+  </si>
+  <si>
+    <t>1020</t>
+  </si>
+  <si>
+    <t>Hinduism</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>Humanism</t>
+  </si>
+  <si>
+    <t>1022</t>
+  </si>
+  <si>
+    <t>Independent</t>
+  </si>
+  <si>
+    <t>1023</t>
+  </si>
+  <si>
+    <t>Islam</t>
+  </si>
+  <si>
+    <t>1024</t>
+  </si>
+  <si>
+    <t>Jainism</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>Jehovah's Witnesses</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>Judaism</t>
+  </si>
+  <si>
+    <t>1027</t>
+  </si>
+  <si>
+    <t>Latter Day Saints</t>
+  </si>
+  <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>Lutheran</t>
+  </si>
+  <si>
+    <t>1029</t>
+  </si>
+  <si>
+    <t>Mahayana</t>
+  </si>
+  <si>
+    <t>1030</t>
+  </si>
+  <si>
+    <t>Meditation</t>
+  </si>
+  <si>
+    <t>1031</t>
+  </si>
+  <si>
+    <t>Messianic Judaism</t>
+  </si>
+  <si>
+    <t>1073</t>
+  </si>
+  <si>
+    <t>Methodist</t>
+  </si>
+  <si>
+    <t>1032</t>
+  </si>
+  <si>
+    <t>Mitraism</t>
+  </si>
+  <si>
+    <t>1074</t>
+  </si>
+  <si>
+    <t>Native American</t>
+  </si>
+  <si>
+    <t>1075</t>
+  </si>
+  <si>
+    <t>Nazarene</t>
+  </si>
+  <si>
+    <t>1033</t>
+  </si>
+  <si>
+    <t>New Age</t>
+  </si>
+  <si>
+    <t>1034</t>
+  </si>
+  <si>
+    <t>non-Roman Catholic</t>
+  </si>
+  <si>
+    <t>1035</t>
+  </si>
+  <si>
+    <t>Occult</t>
+  </si>
+  <si>
+    <t>1036</t>
+  </si>
+  <si>
+    <t>Orthodox</t>
+  </si>
+  <si>
+    <t>1037</t>
+  </si>
+  <si>
+    <t>Paganism</t>
+  </si>
+  <si>
+    <t>1038</t>
+  </si>
+  <si>
+    <t>Pentecostal</t>
+  </si>
+  <si>
+    <t>1076</t>
+  </si>
+  <si>
+    <t>Presbyterian</t>
+  </si>
+  <si>
+    <t>1039</t>
+  </si>
+  <si>
+    <t>Process, The</t>
+  </si>
+  <si>
+    <t>1077</t>
+  </si>
+  <si>
+    <t>Protestant</t>
+  </si>
+  <si>
+    <t>1078</t>
+  </si>
+  <si>
+    <t>Protestant, No Denomination</t>
+  </si>
+  <si>
+    <t>1079</t>
+  </si>
+  <si>
+    <t>Reformed</t>
+  </si>
+  <si>
+    <t>1040</t>
+  </si>
+  <si>
+    <t>Reformed/Presbyterian</t>
+  </si>
+  <si>
+    <t>1041</t>
+  </si>
+  <si>
+    <t>Roman Catholic Church</t>
+  </si>
+  <si>
+    <t>1080</t>
+  </si>
+  <si>
+    <t>Salvation Army</t>
+  </si>
+  <si>
+    <t>1042</t>
+  </si>
+  <si>
+    <t>Satanism</t>
+  </si>
+  <si>
+    <t>1043</t>
+  </si>
+  <si>
+    <t>Scientology</t>
+  </si>
+  <si>
+    <t>1044</t>
+  </si>
+  <si>
+    <t>Shamanism</t>
+  </si>
+  <si>
+    <t>1045</t>
+  </si>
+  <si>
+    <t>Shiite (Islam)</t>
+  </si>
+  <si>
+    <t>1046</t>
+  </si>
+  <si>
+    <t>Shinto</t>
+  </si>
+  <si>
+    <t>1047</t>
+  </si>
+  <si>
+    <t>Sikism</t>
+  </si>
+  <si>
+    <t>1048</t>
+  </si>
+  <si>
+    <t>Spiritualism</t>
+  </si>
+  <si>
+    <t>1049</t>
+  </si>
+  <si>
+    <t>Sunni (Islam)</t>
+  </si>
+  <si>
+    <t>1050</t>
+  </si>
+  <si>
+    <t>Taoism</t>
+  </si>
+  <si>
+    <t>1051</t>
+  </si>
+  <si>
+    <t>Theravada</t>
+  </si>
+  <si>
+    <t>1052</t>
+  </si>
+  <si>
+    <t>Unitarian-Universalism</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>United Church of Christ</t>
+  </si>
+  <si>
+    <t>1053</t>
+  </si>
+  <si>
+    <t>Universal Life Church</t>
+  </si>
+  <si>
+    <t>1054</t>
+  </si>
+  <si>
+    <t>Vajrayana (Tibetan)</t>
+  </si>
+  <si>
+    <t>1055</t>
+  </si>
+  <si>
+    <t>Veda</t>
+  </si>
+  <si>
+    <t>1056</t>
+  </si>
+  <si>
+    <t>Voodoo</t>
+  </si>
+  <si>
+    <t>1057</t>
+  </si>
+  <si>
+    <t>Wicca</t>
+  </si>
+  <si>
+    <t>1058</t>
+  </si>
+  <si>
+    <t>Yaohushua</t>
+  </si>
+  <si>
+    <t>1059</t>
+  </si>
+  <si>
+    <t>Zen Buddhism</t>
+  </si>
+  <si>
+    <t>1060</t>
+  </si>
+  <si>
+    <t>Zoroastrianism</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v3-ReligiousAffiliation</t>
+  </si>
+  <si>
+    <t>ASKU</t>
+  </si>
+  <si>
+    <t>asked but unknown</t>
+  </si>
+  <si>
+    <t>OTH</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>UNK</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v3-NullFlavor</t>
   </si>
 </sst>
 </file>
@@ -790,83 +1299,83 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>12</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>16</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -885,698 +1394,1446 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>35</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>39</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>41</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>55</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>59</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>63</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>65</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>67</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>69</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>77</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>79</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>90</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>102</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>104</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>106</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>112</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>116</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>118</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>120</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>122</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>124</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>126</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>128</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>130</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>132</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>134</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>136</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>138</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>140</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>142</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>144</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>146</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>148</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>150</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>152</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>154</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>156</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>158</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>160</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>162</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>164</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>166</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>168</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>170</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>172</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>174</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>176</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>178</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>180</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>182</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>184</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>186</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>188</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>190</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>192</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>194</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>196</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="B87" t="s" s="2">
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B84"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>199</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>361</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="368">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,10 +81,6 @@
   </si>
   <si>
     <t>Description</t>
-  </si>
-  <si>
-    <t>Navigate to [ConceptMap VF_Religion](ConceptMap-CMVFReligion.html)
-&gt; Note that the FHIR binding is to the codes in the fhir system. The codes from the VistADefinedElements system are map source codes: they may be included in addition to the fhir codes, but they don't address the binding requirement.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1355,28 +1351,26 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
-      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1395,7 +1389,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -1403,666 +1397,666 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>40</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>44</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>46</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>48</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>56</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>58</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>60</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>62</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>64</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>70</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>91</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>103</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>105</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>113</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>115</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>117</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>119</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>121</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>123</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>125</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>127</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>129</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>131</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>133</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>135</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>137</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>139</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>141</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>143</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>145</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>147</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>149</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>151</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>153</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>155</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>157</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>159</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>161</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>163</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>165</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>167</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>169</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>171</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>173</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>175</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>177</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>179</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>181</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>183</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>185</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>187</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>189</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2081,7 +2075,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -2089,690 +2083,690 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>194</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>196</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>198</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>202</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>204</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>208</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>214</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>216</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>218</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>222</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>226</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>234</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>236</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>240</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>242</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>246</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>248</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>250</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>256</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>258</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>260</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>264</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>266</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>268</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>270</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>272</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>276</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>278</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>282</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>288</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>292</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>294</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>298</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>300</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>302</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>304</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>308</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>310</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>314</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>316</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>318</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>320</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>322</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>324</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>326</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>328</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>336</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>338</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>346</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>348</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>350</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>354</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>356</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>358</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>360</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -2791,7 +2785,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -2799,42 +2793,42 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>363</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>367</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="369">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>ValueSet for terminology map VF_Religion</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1351,26 +1354,28 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1394,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -1397,666 +1402,666 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2075,7 +2080,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -2083,690 +2088,690 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -2785,7 +2790,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -2793,42 +2798,42 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -83,7 +83,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet for terminology map VF_Religion</t>
+    <t>ValueSet for Terminology Maps VF_Religion</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -8,14 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from Religious Affili" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from 2-.08" r:id="rId5" sheetId="3"/>
-    <sheet name="Include from NullFlavor" r:id="rId6" sheetId="4"/>
+    <sheet name="Include from NullFlavor" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="200">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -53,13 +52,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -83,7 +82,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet for Terminology Maps VF_Religion</t>
+    <t>FHIR Target ValueSet for Terminology Maps VF_Religion</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -594,513 +593,6 @@
   </si>
   <si>
     <t>http://terminology.hl7.org/CodeSystem/v3-ReligiousAffiliation</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>ADVENTIST</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>AFRICAN RELIGIONS</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>AFRO-CARIBBEAN RELIGIONS</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>AGNOSTICISM</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>ANGLICAN</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>ANIMISM</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>ASSEMBLY OF GOD</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>ATHEISM</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>BABI &amp;amp; BAHA'I FAITHS</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>BAPTIST</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>BON</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>BRETHREN</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>CAO DAI</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>CELTICISM</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>CHRISTIAN (NON-SPECIFIC)</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>CHRISTIAN SCIENTIST</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>CHURCH OF CHRIST</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>CHURCH OF GOD</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>CONFUCIANISM</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>CONGREGATIONAL</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>CYBERCULTURE RELIGIONS</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>DISCIPLES OF CHRIST</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>DIVINATION</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>EASTERN ORTHODOX</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>EPISCOPALIAN</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>EVANGELICAL COVENANT</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>FOURTH WAY</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>FREE DAISM</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>FRIENDS</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>FULL GOSPEL</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>GNOSIS</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>HINDUISM</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>HUMANISM</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>INDEPENDENT</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>ISLAM</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>JAINISM</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>JEHOVAH'S WITNESSES</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>JUDAISM</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>LATTER DAY SAINTS</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>LUTHERAN</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>MAHAYANA</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>MEDITATION</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>MESSIANIC JUDAISM</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>METHODIST</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>MITRAISM</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>NATIVE AMERICAN</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>NAZARENE</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>NEW AGE</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>NON-ROMAN CATHOLIC</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>OCCULT</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>ORTHODOX</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>PAGANISM</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>PENTECOSTAL</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>PRESBYTERIAN</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>PROCESS, THE</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>PROTESTANT</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>PROTESTANT, NO DENOMINATION</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>REFORMED</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>REFORMED/PRESBYTERIAN</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>ROMAN CATHOLIC CHURCH</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>SALVATION ARMY</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>SATANISM</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>SCIENTOLOGY</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>SHAMANISM</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>SHIITE (ISLAM)</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>SHINTO</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>SIKISM</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>SPIRITUALISM</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>SUNNI (ISLAM)</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>TAOISM</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>THERAVADA</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>UNITARIAN-UNIVERSALISM</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>UNITED CHURCH OF CHRIST</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>UNIVERSAL LIFE CHURCH</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>VAJRAYANA (TIBETAN)</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>VEDA</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>VOODOO</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>WICCA</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>YAOHUSHUA</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>ZEN BUDDHISM</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>ZOROASTRIANISM</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>ASKED BUT DECLINED TO ANSWER</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>OTHER</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>UNKNOWN/NO PREFERENCE</t>
-  </si>
-  <si>
-    <t>http://va.gov/terminology/vistaDefinedElements/2-.08</t>
   </si>
   <si>
     <t>ASKU</t>
@@ -2071,716 +1563,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B87"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>361</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -2798,26 +1580,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>362</v>
+        <v>193</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>363</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>364</v>
+        <v>195</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>365</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>366</v>
+        <v>197</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>367</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5">
@@ -2833,7 +1615,7 @@
         <v>191</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>368</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -70,7 +70,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -7,8 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from Religious Affili" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from NullFlavor" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFReligion.xlsx
+++ b/docs/ValueSet-VSVFReligion.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
